--- a/data/trans_dic/IP29_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP29_R-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con lactancia materna exclusiva hasta los 6 primeros meses de vida o más</t>
+          <t>Menores con lactancia materna exclusiva hasta los 6 primeros meses de vida o más (tasa de respuesta: 98,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,72; 33,71</t>
+          <t>19,1; 33,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,93; 45,33</t>
+          <t>27,86; 44,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,57; 40,38</t>
+          <t>24,17; 41,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,83; 38,1</t>
+          <t>22,17; 37,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,08; 24,38</t>
+          <t>11,43; 24,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,42; 42,05</t>
+          <t>25,08; 41,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,84; 32,99</t>
+          <t>22,63; 32,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,69; 33,34</t>
+          <t>21,84; 33,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,55; 38,31</t>
+          <t>27,06; 38,36</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,04; 39,11</t>
+          <t>23,81; 40,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,99; 34,77</t>
+          <t>19,99; 34,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,6; 33,1</t>
+          <t>18,94; 33,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,09; 34,23</t>
+          <t>19,93; 35,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,19; 22,57</t>
+          <t>10,56; 22,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,53; 34,33</t>
+          <t>20,38; 34,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,02; 34,93</t>
+          <t>23,14; 34,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,95; 26,98</t>
+          <t>16,32; 26,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,46; 31,08</t>
+          <t>21,66; 31,25</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,54; 38,21</t>
+          <t>20,69; 38,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,4; 25,78</t>
+          <t>12,59; 26,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,97; 33,38</t>
+          <t>15,75; 33,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20,4; 35,45</t>
+          <t>21,3; 35,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,95; 23,72</t>
+          <t>10,78; 23,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,51; 34,99</t>
+          <t>17,42; 33,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,34; 34,62</t>
+          <t>22,37; 34,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,04; 22,52</t>
+          <t>13,19; 22,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,39; 31,19</t>
+          <t>18,97; 31,15</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,64; 34,17</t>
+          <t>23,81; 34,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,52; 31,54</t>
+          <t>21,31; 31,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,79; 37,57</t>
+          <t>27,58; 37,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,46; 34,88</t>
+          <t>24,14; 34,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,8; 31,89</t>
+          <t>22,41; 32,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,49; 37,45</t>
+          <t>26,44; 37,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,21; 32,49</t>
+          <t>25,49; 32,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,74; 29,99</t>
+          <t>23,38; 30,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28,27; 35,52</t>
+          <t>28,32; 35,82</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,44; 44,23</t>
+          <t>27,95; 44,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23,99; 37,21</t>
+          <t>25,31; 37,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,66; 30,11</t>
+          <t>18,18; 29,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21,83; 34,68</t>
+          <t>21,71; 34,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,68; 36,36</t>
+          <t>23,47; 36,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,9; 37,81</t>
+          <t>25,22; 38,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,13; 37,27</t>
+          <t>26,85; 36,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>25,6; 35,07</t>
+          <t>26,08; 34,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23,4; 32,54</t>
+          <t>23,63; 32,35</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33,33; 52,06</t>
+          <t>33,97; 52,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,56; 26,75</t>
+          <t>8,89; 26,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26,86; 47,57</t>
+          <t>27,26; 46,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24,03; 42,92</t>
+          <t>24,65; 42,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,51; 30,83</t>
+          <t>14,07; 30,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,43; 44,55</t>
+          <t>25,17; 43,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,67; 45,58</t>
+          <t>31,96; 45,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,99; 25,8</t>
+          <t>13,38; 25,75</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27,84; 42,12</t>
+          <t>28,48; 42,5</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>28,22; 34,38</t>
+          <t>28,36; 34,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>24,12; 29,95</t>
+          <t>24,33; 30,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26,41; 32,04</t>
+          <t>26,61; 32,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26,36; 31,71</t>
+          <t>26,23; 31,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,19; 25,61</t>
+          <t>20,52; 25,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,65; 33,39</t>
+          <t>27,53; 33,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,92; 32,17</t>
+          <t>28,16; 32,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,04; 26,75</t>
+          <t>23,12; 27,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>27,86; 32,04</t>
+          <t>27,86; 32,09</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores con lactancia materna exclusiva hasta los 6 primeros meses de vida o más (tasa de respuesta: 98,65%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>25534</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>32266</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>25759</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>27553</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>15304</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>30652</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>53087</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>47570</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>56411</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>18879; 33323</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24682; 39081</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>19621; 33687</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20881; 35318</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>10039; 21463</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>23478; 39256</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>43689; 63043</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>38530; 58830</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>47308; 67054</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>25654</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>24507</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>26001</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>22291</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>14825</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>29779</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>47944</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>39332</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>55780</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>19743; 33279</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>18112; 31340</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>19386; 34149</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>16738; 29462</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>9922; 21163</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>22404; 37692</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>38629; 57277</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>30119; 48245</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>45978; 66340</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>18602</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15585</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14268</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>26683</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>13829</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>19344</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>45285</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>29414</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>33613</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>13529; 24863</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10594; 22044</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9534; 19980</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>20242; 33881</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>9063; 19785</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>13142; 25535</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>35881; 55216</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>22183; 37586</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>25792; 42353</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>54980</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>52402</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>70651</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>55988</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>59735</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>64837</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>110968</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>112137</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>135489</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>45732; 66017</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>42663; 63959</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>59840; 81870</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>46406; 66310</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>49570; 71914</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>54149; 76694</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>97962; 126513</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>98532; 129060</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>119439; 151061</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>35807</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>45550</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>32188</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>34661</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>40931</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>44393</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>70468</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>86481</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>76581</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>27558; 43646</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>37207; 55733</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>24304; 39974</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>27026; 42839</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>32548; 51180</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>35748; 54649</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>59901; 82174</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>74520; 99861</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>65089; 89096</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>31419</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>8333</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>22015</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>22948</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>14761</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>22867</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>54368</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>23094</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>44882</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>24938; 38405</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>4610; 13492</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>16467; 28365</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>16951; 29486</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>9949; 21359</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>16904; 29426</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>45448; 64472</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>16403; 31569</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>36330; 54214</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>476</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>585</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>191996</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>178645</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>190883</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>190124</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>159384</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>211872</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>382120</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>338029</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>402755</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>173340; 210606</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>161175; 199641</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>174319; 211110</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>172744; 209735</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>142950; 178226</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>190677; 233154</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>357542; 407163</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>314119; 369387</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>375478; 432483</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP29_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP29_R-Clase-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,1; 33,71</t>
+          <t>19,3; 33,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,86; 44,11</t>
+          <t>28,38; 45,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,17; 41,5</t>
+          <t>23,93; 41,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,17; 37,49</t>
+          <t>22,12; 37,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,43; 24,44</t>
+          <t>11,23; 24,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,08; 41,93</t>
+          <t>25,46; 40,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,63; 32,66</t>
+          <t>23,24; 33,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,84; 33,35</t>
+          <t>21,73; 32,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,06; 38,36</t>
+          <t>26,61; 38,22</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,81; 40,13</t>
+          <t>22,46; 40,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,99; 34,59</t>
+          <t>19,79; 34,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,94; 33,37</t>
+          <t>18,95; 33,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,93; 35,08</t>
+          <t>19,35; 34,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,56; 22,52</t>
+          <t>10,23; 22,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,38; 34,28</t>
+          <t>21,22; 34,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,14; 34,32</t>
+          <t>23,66; 34,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,32; 26,14</t>
+          <t>16,33; 26,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,66; 31,25</t>
+          <t>21,25; 31,39</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,69; 38,03</t>
+          <t>20,63; 37,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,59; 26,2</t>
+          <t>11,6; 25,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,75; 33,01</t>
+          <t>15,81; 33,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,3; 35,66</t>
+          <t>20,69; 35,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,78; 23,52</t>
+          <t>10,86; 24,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,42; 33,85</t>
+          <t>18,02; 35,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,37; 34,42</t>
+          <t>22,73; 34,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,19; 22,34</t>
+          <t>12,92; 22,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,97; 31,15</t>
+          <t>19,17; 31,25</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,81; 34,38</t>
+          <t>23,68; 33,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,31; 31,95</t>
+          <t>21,42; 31,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,58; 37,73</t>
+          <t>27,6; 38,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,14; 34,5</t>
+          <t>24,31; 34,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,41; 32,52</t>
+          <t>22,72; 32,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,44; 37,45</t>
+          <t>25,99; 37,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,49; 32,92</t>
+          <t>25,28; 32,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,38; 30,63</t>
+          <t>23,16; 30,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28,32; 35,82</t>
+          <t>28,58; 35,63</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>27,95; 44,26</t>
+          <t>28,98; 44,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25,31; 37,92</t>
+          <t>24,99; 37,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,18; 29,9</t>
+          <t>19,06; 30,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21,71; 34,42</t>
+          <t>22,04; 35,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,47; 36,9</t>
+          <t>22,83; 35,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,22; 38,55</t>
+          <t>24,87; 38,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,85; 36,84</t>
+          <t>26,02; 36,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>26,08; 34,95</t>
+          <t>26,48; 35,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23,63; 32,35</t>
+          <t>23,43; 32,28</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33,97; 52,32</t>
+          <t>33,76; 52,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,89; 26,02</t>
+          <t>8,56; 27,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27,26; 46,95</t>
+          <t>26,68; 47,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24,65; 42,87</t>
+          <t>25,09; 43,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14,07; 30,2</t>
+          <t>13,56; 30,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,17; 43,82</t>
+          <t>24,93; 44,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,96; 45,34</t>
+          <t>32,23; 45,5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,38; 25,75</t>
+          <t>13,35; 25,55</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28,48; 42,5</t>
+          <t>28,59; 42,92</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>28,36; 34,46</t>
+          <t>28,45; 34,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>24,33; 30,14</t>
+          <t>24,4; 30,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26,61; 32,22</t>
+          <t>26,01; 31,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26,23; 31,84</t>
+          <t>25,98; 31,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,52; 25,59</t>
+          <t>20,29; 25,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,53; 33,66</t>
+          <t>28,07; 33,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,16; 32,06</t>
+          <t>27,94; 32,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,12; 27,18</t>
+          <t>22,9; 26,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>27,86; 32,09</t>
+          <t>27,87; 31,9</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18879; 33323</t>
+          <t>19083; 33372</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24682; 39081</t>
+          <t>25138; 40719</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19621; 33687</t>
+          <t>19420; 33303</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20881; 35318</t>
+          <t>20837; 35001</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10039; 21463</t>
+          <t>9866; 21723</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23478; 39256</t>
+          <t>23835; 38042</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43689; 63043</t>
+          <t>44864; 64596</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>38530; 58830</t>
+          <t>38333; 57663</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>47308; 67054</t>
+          <t>46504; 66807</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19743; 33279</t>
+          <t>18626; 33241</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18112; 31340</t>
+          <t>17927; 31586</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19386; 34149</t>
+          <t>19392; 34769</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16738; 29462</t>
+          <t>16254; 29048</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9922; 21163</t>
+          <t>9616; 21284</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22404; 37692</t>
+          <t>23336; 38404</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38629; 57277</t>
+          <t>39485; 57446</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30119; 48245</t>
+          <t>30136; 48184</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>45978; 66340</t>
+          <t>45113; 66634</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13529; 24863</t>
+          <t>13486; 24655</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10594; 22044</t>
+          <t>9762; 21620</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9534; 19980</t>
+          <t>9572; 20013</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20242; 33881</t>
+          <t>19661; 33666</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9063; 19785</t>
+          <t>9133; 20541</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13142; 25535</t>
+          <t>13594; 26600</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35881; 55216</t>
+          <t>36453; 55058</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22183; 37586</t>
+          <t>21745; 38365</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25792; 42353</t>
+          <t>26061; 42488</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>45732; 66017</t>
+          <t>45483; 64220</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>42663; 63959</t>
+          <t>42879; 63948</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>59840; 81870</t>
+          <t>59890; 83190</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46406; 66310</t>
+          <t>46735; 66588</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>49570; 71914</t>
+          <t>50239; 72167</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>54149; 76694</t>
+          <t>53221; 76240</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>97962; 126513</t>
+          <t>97123; 125031</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>98532; 129060</t>
+          <t>97591; 128459</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>119439; 151061</t>
+          <t>120553; 150260</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>27558; 43646</t>
+          <t>28575; 43779</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>37207; 55733</t>
+          <t>36735; 55440</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24304; 39974</t>
+          <t>25480; 40483</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27026; 42839</t>
+          <t>27429; 43823</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>32548; 51180</t>
+          <t>31668; 49219</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>35748; 54649</t>
+          <t>35262; 53932</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>59901; 82174</t>
+          <t>58034; 82239</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>74520; 99861</t>
+          <t>75641; 100468</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>65089; 89096</t>
+          <t>64528; 88914</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>24938; 38405</t>
+          <t>24779; 38798</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4610; 13492</t>
+          <t>4441; 14124</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16467; 28365</t>
+          <t>16118; 28448</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16951; 29486</t>
+          <t>17258; 29586</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9949; 21359</t>
+          <t>9592; 21450</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16904; 29426</t>
+          <t>16742; 30103</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>45448; 64472</t>
+          <t>45832; 64687</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16403; 31569</t>
+          <t>16366; 31325</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>36330; 54214</t>
+          <t>36472; 54754</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>173340; 210606</t>
+          <t>173919; 211152</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>161175; 199641</t>
+          <t>161608; 199457</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>174319; 211110</t>
+          <t>170402; 208451</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>172744; 209735</t>
+          <t>171135; 209057</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>142950; 178226</t>
+          <t>141319; 178751</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>190677; 233154</t>
+          <t>194473; 234340</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>357542; 407163</t>
+          <t>354780; 409854</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>314119; 369387</t>
+          <t>311141; 364327</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>375478; 432483</t>
+          <t>375654; 429928</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP29_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP29_R-Clase-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>29,25%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17,43%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>32,74%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>25,83%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>36,42%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>31,74%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>29,25%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>17,43%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>32,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,3; 33,76</t>
+          <t>22,83; 38,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28,38; 45,96</t>
+          <t>11,08; 24,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,93; 41,03</t>
+          <t>25,42; 42,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,12; 37,15</t>
+          <t>18,72; 33,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,23; 24,74</t>
+          <t>27,93; 45,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,46; 40,63</t>
+          <t>23,57; 40,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,24; 33,46</t>
+          <t>22,84; 32,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,73; 32,69</t>
+          <t>21,69; 33,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,61; 38,22</t>
+          <t>26,55; 38,31</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>26,54%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15,77%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>27,08%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>30,94%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>27,05%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>25,41%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>26,54%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>15,77%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>27,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,46; 40,09</t>
+          <t>19,09; 34,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,79; 34,86</t>
+          <t>10,19; 22,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,95; 33,97</t>
+          <t>20,53; 34,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,35; 34,59</t>
+          <t>23,04; 39,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,23; 22,65</t>
+          <t>19,99; 34,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,22; 34,93</t>
+          <t>18,6; 33,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,66; 34,42</t>
+          <t>23,02; 34,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,33; 26,1</t>
+          <t>16,95; 26,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,25; 31,39</t>
+          <t>21,46; 31,08</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>28,08%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16,44%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>25,65%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>28,45%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>18,53%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>23,57%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>28,08%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>16,44%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>25,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,63; 37,71</t>
+          <t>20,4; 35,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,6; 25,7</t>
+          <t>10,95; 23,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,81; 33,07</t>
+          <t>18,51; 34,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20,69; 35,43</t>
+          <t>20,54; 38,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,86; 24,42</t>
+          <t>12,4; 25,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,02; 35,27</t>
+          <t>14,97; 33,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,73; 34,32</t>
+          <t>22,34; 34,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,92; 22,8</t>
+          <t>13,04; 22,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,17; 31,25</t>
+          <t>19,39; 31,19</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>29,13%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>27,01%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>31,66%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>28,63%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>26,18%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>32,56%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>29,13%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>27,01%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>31,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,68; 33,44</t>
+          <t>24,46; 34,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,42; 31,94</t>
+          <t>21,8; 31,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,6; 38,34</t>
+          <t>26,49; 37,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,31; 34,64</t>
+          <t>23,64; 34,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,72; 32,63</t>
+          <t>21,52; 31,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,99; 37,23</t>
+          <t>27,79; 37,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,28; 32,54</t>
+          <t>25,21; 32,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,16; 30,49</t>
+          <t>22,74; 29,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28,58; 35,63</t>
+          <t>28,27; 35,52</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>27,85%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>29,51%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>31,31%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>36,31%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>30,99%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>24,08%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>27,85%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>29,51%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>31,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,98; 44,4</t>
+          <t>21,83; 34,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24,99; 37,72</t>
+          <t>23,68; 36,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,06; 30,28</t>
+          <t>23,9; 37,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,04; 35,21</t>
+          <t>28,44; 44,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,83; 35,48</t>
+          <t>23,99; 37,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,87; 38,04</t>
+          <t>18,66; 30,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,02; 36,87</t>
+          <t>27,13; 37,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>26,48; 35,17</t>
+          <t>25,6; 35,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23,43; 32,28</t>
+          <t>23,4; 32,54</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>33,37%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>20,87%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>34,05%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>42,8%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>16,07%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>36,44%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>33,37%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>20,87%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>34,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33,76; 52,86</t>
+          <t>24,03; 42,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,56; 27,24</t>
+          <t>13,51; 30,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26,68; 47,09</t>
+          <t>25,43; 44,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25,09; 43,02</t>
+          <t>33,33; 52,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,56; 30,32</t>
+          <t>8,56; 26,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,93; 44,83</t>
+          <t>26,86; 47,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,23; 45,5</t>
+          <t>31,67; 45,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,35; 25,55</t>
+          <t>12,99; 25,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28,59; 42,92</t>
+          <t>27,84; 42,12</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>28,86%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>22,88%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>30,59%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>31,41%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>26,97%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>29,14%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>28,86%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>22,88%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>30,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>28,45; 34,55</t>
+          <t>26,36; 31,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>24,4; 30,11</t>
+          <t>20,19; 25,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26,01; 31,82</t>
+          <t>27,65; 33,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25,98; 31,74</t>
+          <t>28,22; 34,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,29; 25,66</t>
+          <t>24,12; 29,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,07; 33,83</t>
+          <t>26,41; 32,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,94; 32,27</t>
+          <t>27,92; 32,17</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>22,9; 26,81</t>
+          <t>23,04; 26,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>27,87; 31,9</t>
+          <t>27,86; 32,04</t>
         </is>
       </c>
     </row>
@@ -1438,14 +1438,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1533,32 +1533,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>40</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>27553</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15304</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>30652</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>25534</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>32266</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>25759</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>27553</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>15304</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>30652</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19083; 33372</t>
+          <t>21505; 35889</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25138; 40719</t>
+          <t>9734; 21410</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19420; 33303</t>
+          <t>23797; 39371</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20837; 35001</t>
+          <t>18508; 33323</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9866; 21723</t>
+          <t>24741; 40162</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23835; 38042</t>
+          <t>19132; 32773</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44864; 64596</t>
+          <t>44089; 63698</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>38333; 57663</t>
+          <t>38260; 58815</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>46504; 66807</t>
+          <t>46407; 66961</t>
         </is>
       </c>
     </row>
@@ -1696,32 +1696,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>39</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1749,32 +1749,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>22291</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14825</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>29779</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>25654</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>24507</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>26001</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>22291</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>14825</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>29779</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18626; 33241</t>
+          <t>16031; 28750</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17927; 31586</t>
+          <t>9577; 21215</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19392; 34769</t>
+          <t>22573; 37741</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16254; 29048</t>
+          <t>19108; 32432</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9616; 21284</t>
+          <t>18111; 31498</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23336; 38404</t>
+          <t>19036; 33870</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39485; 57446</t>
+          <t>38415; 58300</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30136; 48184</t>
+          <t>31280; 49802</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>45113; 66634</t>
+          <t>45560; 65991</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1912,32 +1912,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>26683</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>13829</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>19344</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>18602</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>15585</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>14268</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>26683</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>13829</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>19344</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13486; 24655</t>
+          <t>19381; 33684</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9762; 21620</t>
+          <t>9208; 19955</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9572; 20013</t>
+          <t>13962; 26395</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19661; 33666</t>
+          <t>13433; 24986</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9133; 20541</t>
+          <t>10433; 21687</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13594; 26600</t>
+          <t>9058; 20202</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36453; 55058</t>
+          <t>35832; 55531</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21745; 38365</t>
+          <t>21942; 37881</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26061; 42488</t>
+          <t>26368; 42406</t>
         </is>
       </c>
     </row>
@@ -2022,32 +2022,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>106</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>55988</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>59735</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>64837</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>54980</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>52402</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>70651</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>55988</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>59735</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>64837</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>45483; 64220</t>
+          <t>47012; 67039</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>42879; 63948</t>
+          <t>48214; 70523</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>59890; 83190</t>
+          <t>54251; 76688</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46735; 66588</t>
+          <t>45395; 65613</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>50239; 72167</t>
+          <t>43083; 63136</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>53221; 76240</t>
+          <t>60305; 81515</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>97123; 125031</t>
+          <t>96862; 124855</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>97591; 128459</t>
+          <t>95811; 126362</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>120553; 150260</t>
+          <t>119233; 149821</t>
         </is>
       </c>
     </row>
@@ -2190,27 +2190,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>50</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2238,32 +2238,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>34661</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>40931</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>44393</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>35807</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>45550</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>32188</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>34661</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>40931</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>44393</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>28575; 43779</t>
+          <t>27167; 43161</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>36735; 55440</t>
+          <t>32842; 50430</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25480; 40483</t>
+          <t>33881; 53596</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27429; 43823</t>
+          <t>28042; 43615</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>31668; 49219</t>
+          <t>35264; 54689</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>35262; 53932</t>
+          <t>24950; 40259</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>58034; 82239</t>
+          <t>60520; 83151</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>75641; 100468</t>
+          <t>73127; 100207</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>64528; 88914</t>
+          <t>64466; 89622</t>
         </is>
       </c>
     </row>
@@ -2348,32 +2348,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2401,32 +2401,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>22948</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>14761</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>22867</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>31419</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>8333</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>22015</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>22948</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>14761</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>22867</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>24779; 38798</t>
+          <t>16524; 29521</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4441; 14124</t>
+          <t>9559; 21808</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16118; 28448</t>
+          <t>17080; 29915</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17258; 29586</t>
+          <t>24463; 38213</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9592; 21450</t>
+          <t>4441; 13871</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16742; 30103</t>
+          <t>16227; 28739</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>45832; 64687</t>
+          <t>45034; 64813</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16366; 31325</t>
+          <t>15929; 31628</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>36472; 54754</t>
+          <t>35510; 53730</t>
         </is>
       </c>
     </row>
@@ -2511,32 +2511,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>255</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>289</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>296</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>190124</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>159384</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>211872</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>191996</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>178645</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>190883</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>190124</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>159384</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>211872</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>173919; 211152</t>
+          <t>173645; 208841</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>161608; 199457</t>
+          <t>140605; 178350</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>170402; 208451</t>
+          <t>191512; 231316</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>171135; 209057</t>
+          <t>172484; 210110</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>141319; 178751</t>
+          <t>159772; 198345</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>194473; 234340</t>
+          <t>173047; 209873</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>354780; 409854</t>
+          <t>354579; 408546</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>311141; 364327</t>
+          <t>313121; 363551</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>375654; 429928</t>
+          <t>375454; 431836</t>
         </is>
       </c>
     </row>
